--- a/entrega-2/05-reportes-de-defectos-exp.xlsx
+++ b/entrega-2/05-reportes-de-defectos-exp.xlsx
@@ -812,7 +812,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="225" customHeight="1">
+    <row r="24" ht="240" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
@@ -826,7 +826,7 @@
 - Caso de prueba: CP-EXP-062 (también quita valor a CP-EXP-070)
 - Encontrado en: ejecución de CP-EXP-062 (Entrega 2).
 - Reportó: Claude Code (IA), supervisado por Santiago
-- Evidencia: Captura evidencia/CP-EXP-062.jpg (hoja abierta tras el clic) y document.elementFromPoint(5, 5) = DIV.fixed.inset-0.-z-10.bg-[rgba(43,30,25,0.32)], aria-hidden=true
+- Evidencia: Observado en la corrida de CP-EXP-062: la hoja sigue abierta tras el clic; document.elementFromPoint(5, 5) = DIV.fixed.inset-0.-z-10.bg-[rgba(43,30,25,0.32)], aria-hidden=true
 - Causa probable: en src/components/transactions/ExportTransactionsDialog.tsx el cierre por clic exige e.target === e.currentTarget, pero el div de fondo es hijo del contenedor y cubre toda la pantalla: recibe el clic y el destino nunca coincide. No se corrigió nada.</t>
         </is>
       </c>
@@ -1006,7 +1006,7 @@
 - Caso de prueba: CP-EXP-063 y CP-EXP-065
 - Encontrado en: ejecución de CP-EXP-063 y CP-EXP-065 (Entrega 2).
 - Reportó: Claude Code (IA), supervisado por Santiago
-- Evidencia: Capturas evidencia/CP-EXP-063.jpg y evidencia/CP-EXP-065.jpg (URL cambiada con la hoja abierta); log de popstate: ['popstate@?period=2026-08']
+- Evidencia: Observado en las corridas de CP-EXP-063 y CP-EXP-065: URL cambiada con la hoja abierta; log de popstate: ['popstate@?period=2026-08']
 - Causa no determinada. En ExportTransactionsDialog.tsx hay un efecto que cierra la hoja cuando cambia location.key y un oyente de popstate; ninguno logra cerrarla. Hipótesis sin confirmar: el efecto que reinicia initialLocationKeyRef cuando cambia location.key corre antes del que compara la clave y la deja siempre igual. No se corrigió nada.</t>
         </is>
       </c>
@@ -1186,7 +1186,7 @@
 - Caso de prueba: CP-EXP-064
 - Encontrado en: ejecución de CP-EXP-064 (Entrega 2).
 - Reportó: Claude Code (IA), supervisado por Santiago
-- Evidencia: Captura evidencia/CP-EXP-064.jpg (aviso de éxito en el período anterior); descargas registradas por el navegador = 1
+- Evidencia: Observado en la corrida de CP-EXP-064: aviso de éxito en el período anterior; descargas registradas por el navegador = 1
 - Relacionado con DEF-031: el cierre por «Atrás» no llega a abortar la exportación en curso (AbortController). No se investigó a fondo. No se corrigió nada.</t>
         </is>
       </c>
